--- a/selenium-tests/Login_E2E_Test_Report_300.xlsx
+++ b/selenium-tests/Login_E2E_Test_Report_300.xlsx
@@ -17,7 +17,7 @@
     <t>TURFINGTON WEB FRONTEND - SELENIUM E2E TEST EXECUTION SUMMARY</t>
   </si>
   <si>
-    <t>Authentication &amp; Login Functional Automation Run • Generated on 10/21/2026, 1:45:57 PM GMT+5:30</t>
+    <t>Authentication &amp; Login Functional Automation Run • Generated on 10/30/2026, 11:56:05 PM GMT+5:30</t>
   </si>
   <si>
     <t>TOTAL TEST CASES</t>

--- a/selenium-tests/Login_E2E_Test_Report_300.xlsx
+++ b/selenium-tests/Login_E2E_Test_Report_300.xlsx
@@ -17,7 +17,7 @@
     <t>TURFINGTON WEB FRONTEND - SELENIUM E2E TEST EXECUTION SUMMARY</t>
   </si>
   <si>
-    <t>Authentication &amp; Login Functional Automation Run • Generated on 10/30/2026, 11:56:05 PM GMT+5:30</t>
+    <t>Authentication &amp; Login Functional Automation Run • Generated on 10/31/2026, 1:03:58 AM GMT+5:30</t>
   </si>
   <si>
     <t>TOTAL TEST CASES</t>

--- a/selenium-tests/Login_E2E_Test_Report_300.xlsx
+++ b/selenium-tests/Login_E2E_Test_Report_300.xlsx
@@ -17,7 +17,7 @@
     <t>TURFINGTON WEB FRONTEND - SELENIUM E2E TEST EXECUTION SUMMARY</t>
   </si>
   <si>
-    <t>Authentication &amp; Login Functional Automation Run • Generated on 10/31/2026, 1:03:58 AM GMT+5:30</t>
+    <t>Authentication &amp; Login Functional Automation Run • Generated on 10/31/2026, 1:02:29 PM GMT+5:30</t>
   </si>
   <si>
     <t>TOTAL TEST CASES</t>
